--- a/Sheets/Tasks.xlsx
+++ b/Sheets/Tasks.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samuelgrant/Documents/gm2/EDM/Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8609F8B4-074D-114D-A301-C6187777A562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EC5056-739B-A648-B48F-3B1EA7C6B7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{6384AAE9-1B75-6A45-B9F1-0D53D6F5A28C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>Analysis tasks</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>1 hour</t>
-  </si>
-  <si>
-    <t>Adjust radial field estimates based on empirical method</t>
   </si>
   <si>
     <t>Moderate</t>
@@ -141,19 +138,6 @@
   </si>
   <si>
     <t xml:space="preserve">1 day </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Chapter 2: Move simulation work to simulation chapter. Add discussion on the variation of average EDM vertical angle at maximum tilt, and how this relates to the dilution of the angle. Also summarise the chapter. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t xml:space="preserve">Lab/rest frame notation is currently confusing. We need lab to be default, but annoyingly the lab frame tilt angle has long been called delta prime. </t>
-    </r>
   </si>
   <si>
     <t>Momentum ranges? This has been a bit vague thus far. I tried basing on it on the A_EDM values with the lowest uncertainty,  which is 750-2750 MeV. However, the offset diverges at 750-1000 MeV and we have a population of lost muons beyond 2500, so maybe this is the ideal range? Really, just pick a range of momentum which looks flat. Go with 1000-2500 MeV.</t>
@@ -202,14 +186,132 @@
     <t xml:space="preserve">Include temperature plot as well </t>
   </si>
   <si>
-    <t>Acceptance uncertainty:  1) Use the ratio of the weighted and unweighted points for your ratio, the uncertainty will be binomial (don't understand how to use this or why it's a binomial, just take the larger one). Use this uncertainty in the way you were doing previously, which will give you an overestimated uncertainty based on the difference from the central value; 2) Take the ratio between truth vertices and unweighted sample, propagate through analysis: how do your central values change?; 3) Make ratios using shifted samples, how to the central values change in this case? The resulting shift gives you a shift per mm vertical misalignment. This makes the assumption that the error bars are 100% correlated. These acceptance uncertainties should be derived from simulation in my mind, and should be constant through each dataset. That way they're 100% correlated through each dataset and it's just easier to deal with.</t>
+    <r>
+      <t xml:space="preserve">Acceptance uncertainty: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> 1) Use the ratio of the weighted and unweighted points for your ratio, the uncertainty will be binomial (don't understand how to use this or why it's a binomial, just take the larger one). Use this uncertainty in the way you were doing previously, which will give you an overestimated uncertainty based on the difference from the central value; 2) Take the ratio between truth vertices and unweighted sample, propagate through analysis: how do your central values change?; 3) Make ratios using shifted samples, how to the central values change in this case? The resulting shift gives you a shift per mm vertical misalignment. This makes the assumption that the error bars are 100% correlated. These acceptance uncertainties should be derived from simulation in my mind, and should be constant through each dataset. That way they're 100% correlated through each dataset and it's just easier to deal with. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">1) Use truth vertices ratio. 2) Varying weightings according to gaussian errors in 1000 trials 3) Report width of delta histogram as stat error on acceptance correction. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adjust radial field estimates based on empirical method. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Also need to write up the emprical method bit and update note. We're actually overestimating the uncertainties a bit here, since err_k is correlated with BrBkgErr, but whatever?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BAM: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1) Run simultanous fits over 1000-2500 MeV; 2) Run time dependant offset over 1000-2500 MeV (a bit unneccesary but whatever); 2) Put time dependant offset in slides, note that it has a negligable effect; 3) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Re-run radial field results</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; 4) Reproduce momentum binning illustration; 5) Get phase plots; 6) Produce final table of results and uncertainties. 7) Misalignment error / mm;  8)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Put Joe function on slides. 8) Comment on MC, how many quality tracks do you have?</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 10) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">update radial field note and update so you can link it. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chapter 2: Move simulation work to simulation chapter. Add discussion on the variation of average EDM vertical angle at maximum tilt, and how this relates to the dilution of the angle. Also summarise the chapter. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Lab/rest frame notation is currently confusing. We need lab to be default, but annoyingly the lab frame tilt angle has long been called delta prime.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -254,6 +356,19 @@
       <color rgb="FF00B050"/>
       <name val="Calibri (Body)"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -290,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -332,6 +447,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -653,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05AC189-A4DD-E246-9322-09CDFBAE4BD5}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="40.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="54.33203125" style="3" customWidth="1"/>
@@ -678,224 +802,235 @@
       <c r="B2" s="2"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" ht="272" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="323" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C4" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="C6" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5" t="s">
+    <row r="15" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>16</v>
+      <c r="C18" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>28</v>
+      <c r="A19" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>19</v>
+      <c r="A20" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="11"/>
+      <c r="C22" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="B23" s="11"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
+      <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Sheets/Tasks.xlsx
+++ b/Sheets/Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samuelgrant/Documents/gm2/EDM/Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EC5056-739B-A648-B48F-3B1EA7C6B7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E24DCE7-AD22-5646-806F-83188E9877A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{6384AAE9-1B75-6A45-B9F1-0D53D6F5A28C}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
   <si>
     <t>Analysis tasks</t>
   </si>
@@ -146,165 +146,228 @@
     <t xml:space="preserve">Estimation of blind limit with the analysis in current state. </t>
   </si>
   <si>
+    <t>What is my resolution uncertainty? This just moves the momentum by 1.5% or something. Get momentum plot of meas - truth. We're binning so coarsely it shouldn't matter.</t>
+  </si>
+  <si>
+    <t>Ic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Include temperature plot as well </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chapter 2: Move simulation work to simulation chapter. Add discussion on the variation of average EDM vertical angle at maximum tilt, and how this relates to the dilution of the angle. Also summarise the chapter. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Lab/rest frame notation is currently confusing. We need lab to be default, but annoyingly the lab frame tilt angle has long been called delta prime.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BAM: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1) Run simultanous fits over 1000-2500 MeV; 2) Run time dependant offset over 1000-2500 MeV (a bit unneccesary but whatever); 2) Put time dependant offset in slides, note that it has a negligable effect; 3) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Re-run radial field results</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; 4) Reproduce momentum binning illustration; 5) Get phase plots; 6) Produce final table of results and uncertainties. 7) Misalignment error / mm;  8)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Put Joe function on slides. 8) Comment on MC, how many quality tracks do you have?</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 10) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">update radial field note and update so you can link it. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Acceptance uncertainty: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> 1) Use the ratio of the weighted and unweighted points for your ratio, the uncertainty will be binomial (don't understand how to use this or why it's a binomial, just take the larger one). Use this uncertainty in the way you were doing previously, which will give you an overestimated uncertainty based on the difference from the central value; 2) Take the ratio between truth vertices and unweighted sample, propagate through analysis: how do your central values change?; 3) Make ratios using shifted samples, how to the central values change in this case? The resulting shift gives you a shift per mm vertical misalignment. This makes the assumption that the error bars are 100% correlated. These acceptance uncertainties should be derived from simulation in my mind, and should be constant through each dataset. That way they're 100% correlated through each dataset and it's just easier to deal with. 1) Use truth vertices ratio. 2) Varying weightings according to gaussian errors in 1000 trials 3) Report width of delta histogram as stat error on acceptance correction. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Can we just get an absolute value in mrad, somehow?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Everything will start to break down as you approach zero angle.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adjust radial field estimates based on empirical method. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Also need to write up the emprical method bit and update note. We're actually overestimating the uncertainties a bit here, since err_k is correlated with BrBkgErr, but whatever?</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Estimate a combined uncertainty across datasets. It's fine to combine the way you're doing it. </t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <color rgb="FF00B050"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri (Body)"/>
       </rPr>
       <t>Adjust error bars to include stat and syst so that people can see that it's not massively correlated.</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>Assume that errors are 100% correlated, use same method that Alex uses in his omega_a combination. I'm not sure what "j" is in his summation of errors. Messaged him.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Time randomisation of the VCBO. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">Run </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve">1 phases: I seem to be getting these a bit wrong… </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>What happens if you use the correct Run-1 phase? An incorrect phase could result in a false signal. Seems to make no difference</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Assume that errors are 100% correlated, use same method that Alex uses in his omega_a combination. I'm not sure what "j" is in his summation of errors. Messaged him.</t>
-    </r>
-  </si>
-  <si>
-    <t>What is my resolution uncertainty? This just moves the momentum by 1.5% or something. Get momentum plot of meas - truth. We're binning so coarsely it shouldn't matter.</t>
-  </si>
-  <si>
-    <t>Ic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include temperature plot as well </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Acceptance uncertainty: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t xml:space="preserve"> 1) Use the ratio of the weighted and unweighted points for your ratio, the uncertainty will be binomial (don't understand how to use this or why it's a binomial, just take the larger one). Use this uncertainty in the way you were doing previously, which will give you an overestimated uncertainty based on the difference from the central value; 2) Take the ratio between truth vertices and unweighted sample, propagate through analysis: how do your central values change?; 3) Make ratios using shifted samples, how to the central values change in this case? The resulting shift gives you a shift per mm vertical misalignment. This makes the assumption that the error bars are 100% correlated. These acceptance uncertainties should be derived from simulation in my mind, and should be constant through each dataset. That way they're 100% correlated through each dataset and it's just easier to deal with. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t xml:space="preserve">1) Use truth vertices ratio. 2) Varying weightings according to gaussian errors in 1000 trials 3) Report width of delta histogram as stat error on acceptance correction. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Adjust radial field estimates based on empirical method. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Also need to write up the emprical method bit and update note. We're actually overestimating the uncertainties a bit here, since err_k is correlated with BrBkgErr, but whatever?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">BAM: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1) Run simultanous fits over 1000-2500 MeV; 2) Run time dependant offset over 1000-2500 MeV (a bit unneccesary but whatever); 2) Put time dependant offset in slides, note that it has a negligable effect; 3) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Re-run radial field results</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>; 4) Reproduce momentum binning illustration; 5) Get phase plots; 6) Produce final table of results and uncertainties. 7) Misalignment error / mm;  8)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Put Joe function on slides. 8) Comment on MC, how many quality tracks do you have?</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 10) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t xml:space="preserve">update radial field note and update so you can link it. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Chapter 2: Move simulation work to simulation chapter. Add discussion on the variation of average EDM vertical angle at maximum tilt, and how this relates to the dilution of the angle. Also summarise the chapter. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>Lab/rest frame notation is currently confusing. We need lab to be default, but annoyingly the lab frame tilt angle has long been called delta prime.</t>
-    </r>
+  </si>
+  <si>
+    <t>What's up with the deviation between Run-1a/b and Run-1c/d? You need fit start time scans., more FFTs, take a look at &lt;theta_y&gt; vs momenutm in Run-2</t>
   </si>
 </sst>
 </file>
@@ -353,11 +416,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -368,6 +426,14 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -405,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -449,13 +515,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -777,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05AC189-A4DD-E246-9322-09CDFBAE4BD5}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="40.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="54.33203125" style="3" customWidth="1"/>
@@ -798,239 +867,255 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" ht="153" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A4" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" ht="153" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="356" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="68" x14ac:dyDescent="0.2">
+      <c r="A10" s="15" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="323" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="68" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="B12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="7"/>
-    </row>
-    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
+      <c r="A17" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="11"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="11"/>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
